--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -962,11 +962,34 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://loinc.org"/&gt;
-  &lt;code value="11524-6"/&gt;
-  &lt;display value="EKG Study"/&gt;
-&lt;/valueCoding&gt;</t>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Loinc_CS</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>11524-6</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>EKG Study</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1958,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP69"/>
+  <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.17578125" customWidth="true" bestFit="true"/>
@@ -5899,7 +5922,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -5976,10 +5999,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5999,23 +6022,19 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6063,7 +6082,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>212</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6075,7 +6094,7 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6084,10 +6103,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6098,21 +6117,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6121,23 +6140,21 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>308</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>215</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>216</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6173,46 +6190,46 @@
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>218</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>314</v>
+        <v>213</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6220,10 +6237,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6234,7 +6251,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6246,24 +6263,26 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>318</v>
+        <v>238</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>318</v>
+        <v>239</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6305,13 +6324,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>243</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6326,13 +6345,13 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
@@ -6340,14 +6359,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6366,20 +6385,18 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>323</v>
+        <v>209</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6427,7 +6444,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>251</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6442,19 +6459,19 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>328</v>
+        <v>252</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6462,14 +6479,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6488,26 +6505,24 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>256</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>336</v>
+        <v>258</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>83</v>
@@ -6549,7 +6564,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>260</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6564,19 +6579,19 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>338</v>
+        <v>261</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>339</v>
+        <v>262</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>340</v>
+        <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -6584,10 +6599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6610,18 +6625,18 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>342</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>265</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6630,7 +6645,7 @@
         <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>83</v>
@@ -6669,7 +6684,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6690,13 +6705,13 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>345</v>
+        <v>270</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>346</v>
+        <v>271</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6704,10 +6719,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6718,7 +6733,7 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
@@ -6730,19 +6745,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>349</v>
+        <v>274</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>275</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
+        <v>276</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>351</v>
+        <v>277</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>352</v>
+        <v>278</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6791,13 +6806,13 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>83</v>
@@ -6806,19 +6821,19 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>280</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>281</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -6826,10 +6841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6852,19 +6867,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>358</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>283</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>359</v>
+        <v>284</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>360</v>
+        <v>285</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>361</v>
+        <v>286</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6913,7 +6928,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6922,7 +6937,7 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -6931,27 +6946,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>363</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>365</v>
+        <v>289</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6971,22 +6986,22 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>369</v>
+        <v>319</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7011,13 +7026,13 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7035,7 +7050,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7044,25 +7059,25 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>137</v>
+        <v>322</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7070,14 +7085,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7093,23 +7108,21 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>201</v>
+        <v>326</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7133,11 +7146,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7155,7 +7170,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7173,38 +7188,38 @@
         <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>298</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>384</v>
+        <v>329</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7213,22 +7228,22 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>387</v>
+        <v>332</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>333</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>388</v>
+        <v>333</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>389</v>
+        <v>334</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>390</v>
+        <v>335</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7277,13 +7292,13 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
@@ -7292,19 +7307,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>391</v>
+        <v>337</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>392</v>
+        <v>338</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>83</v>
+        <v>339</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7312,14 +7327,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7335,21 +7350,23 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>201</v>
+        <v>342</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7373,13 +7390,13 @@
         <v>83</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>398</v>
+        <v>83</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>83</v>
@@ -7397,7 +7414,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7412,30 +7429,30 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>401</v>
+        <v>348</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7455,23 +7472,21 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>201</v>
+        <v>351</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7495,13 +7510,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>407</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -7519,7 +7534,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7540,13 +7555,13 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>409</v>
+        <v>354</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>410</v>
+        <v>355</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7554,10 +7569,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7568,7 +7583,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7577,21 +7592,23 @@
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>358</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>359</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>359</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7639,13 +7656,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7654,30 +7671,30 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>416</v>
+        <v>363</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>417</v>
+        <v>364</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>83</v>
+        <v>365</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7697,21 +7714,23 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>420</v>
+        <v>367</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7759,7 +7778,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7768,7 +7787,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7777,27 +7796,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>426</v>
+        <v>375</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7808,7 +7827,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7820,19 +7839,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>428</v>
+        <v>201</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>430</v>
+        <v>378</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>431</v>
+        <v>379</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7857,13 +7876,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7881,19 +7900,19 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>432</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>83</v>
@@ -7902,10 +7921,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>433</v>
+        <v>137</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>434</v>
+        <v>384</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7916,21 +7935,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7942,16 +7961,20 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>210</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7975,13 +7998,11 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7999,49 +8020,49 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>212</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>213</v>
+        <v>393</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8060,18 +8081,20 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>396</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>215</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>216</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8119,7 +8142,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>218</v>
+        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8131,7 +8154,7 @@
         <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>83</v>
@@ -8140,10 +8163,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>213</v>
+        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8154,46 +8177,44 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8217,13 +8238,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8241,45 +8262,45 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>441</v>
+        <v>402</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>83</v>
+        <v>408</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>137</v>
+        <v>410</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8302,16 +8323,20 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>443</v>
+        <v>201</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8335,13 +8360,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>83</v>
+        <v>416</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>83</v>
+        <v>417</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8359,7 +8384,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8368,7 +8393,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>446</v>
+        <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8380,10 +8405,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8394,10 +8419,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8420,15 +8445,17 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8477,7 +8504,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8486,7 +8513,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>446</v>
+        <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8495,27 +8522,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>83</v>
+        <v>424</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8538,20 +8565,18 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>201</v>
+        <v>429</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8575,13 +8600,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8599,7 +8624,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8617,27 +8642,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>83</v>
+        <v>435</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8660,19 +8685,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>437</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8697,13 +8722,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>468</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8721,7 +8746,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8733,19 +8758,19 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>441</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>384</v>
+        <v>443</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8756,10 +8781,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8782,18 +8807,16 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>470</v>
+        <v>209</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>471</v>
+        <v>210</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>472</v>
+        <v>211</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -8841,7 +8864,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>469</v>
+        <v>212</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8853,7 +8876,7 @@
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8865,7 +8888,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>474</v>
+        <v>213</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8876,21 +8899,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
@@ -8902,15 +8925,17 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>476</v>
+        <v>215</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8959,19 +8984,19 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>218</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
@@ -8980,10 +9005,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>447</v>
+        <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>478</v>
+        <v>213</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -8994,14 +9019,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>83</v>
+        <v>447</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9014,24 +9039,26 @@
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>480</v>
+        <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9079,7 +9106,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9091,7 +9118,7 @@
         <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>83</v>
@@ -9100,10 +9127,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>483</v>
+        <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>484</v>
+        <v>137</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9114,10 +9141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9128,7 +9155,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
@@ -9137,20 +9164,18 @@
         <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>487</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9199,16 +9224,16 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9220,10 +9245,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9234,10 +9259,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9248,7 +9273,7 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>83</v>
@@ -9257,23 +9282,19 @@
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9321,16 +9342,16 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9342,10 +9363,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9356,10 +9377,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9382,16 +9403,20 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>210</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9415,13 +9440,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>83</v>
+        <v>467</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9439,7 +9464,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>212</v>
+        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9451,19 +9476,19 @@
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>213</v>
+        <v>393</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9474,14 +9499,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9500,18 +9525,20 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>215</v>
+        <v>472</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>216</v>
+        <v>473</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -9535,13 +9562,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>83</v>
+        <v>476</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>83</v>
+        <v>477</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9559,7 +9586,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>218</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9571,19 +9598,19 @@
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>213</v>
+        <v>393</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9594,45 +9621,43 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>139</v>
+        <v>479</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>162</v>
+        <v>482</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9681,19 +9706,19 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>478</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>83</v>
@@ -9705,7 +9730,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>137</v>
+        <v>483</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9716,10 +9741,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9727,7 +9752,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>94</v>
@@ -9739,23 +9764,19 @@
         <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
@@ -9779,11 +9800,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9801,10 +9824,10 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>94</v>
@@ -9819,16 +9842,16 @@
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>298</v>
+        <v>456</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>299</v>
+        <v>487</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9836,10 +9859,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9850,7 +9873,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -9862,20 +9885,18 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>358</v>
+        <v>489</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
@@ -9923,13 +9944,13 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
@@ -9941,27 +9962,27 @@
         <v>83</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>508</v>
+        <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>364</v>
+        <v>492</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>365</v>
+        <v>493</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9972,7 +9993,7 @@
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>83</v>
@@ -9981,23 +10002,21 @@
         <v>83</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>201</v>
+        <v>495</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
@@ -10021,13 +10040,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10045,16 +10064,16 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10066,10 +10085,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>137</v>
+        <v>492</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>375</v>
+        <v>498</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10080,14 +10099,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10103,22 +10122,22 @@
         <v>83</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>201</v>
+        <v>437</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10143,11 +10162,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10165,7 +10186,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10183,27 +10204,27 @@
         <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>383</v>
+        <v>503</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>384</v>
+        <v>504</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10214,7 +10235,7 @@
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>83</v>
@@ -10226,20 +10247,16 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>519</v>
+        <v>210</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10287,36 +10304,884 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y72" s="2"/>
+      <c r="Z72" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
+      <c r="B74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
+      <c r="H75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="Y75" s="2"/>
+      <c r="Z75" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP69" t="s" s="2">
+      <c r="AK75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="542">
   <si>
     <t>Property</t>
   </si>
@@ -926,67 +926,97 @@
     <t>心電図検査を示すコード</t>
   </si>
   <si>
+    <t>observationの意味を正しく理解するには、すべてのcode-valueペアと、さらに存在する場合にはcomponent.code-component.valueのペアが、考慮される必要がある。</t>
+  </si>
+  <si>
+    <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:ekgCode</t>
+  </si>
+  <si>
+    <t>ekgCode</t>
+  </si>
+  <si>
     <t>心電図検査(EKG Study)を示すLOINCコード 11524-6 を固定値として指定する。</t>
   </si>
   <si>
-    <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
+    <t>Observation.code.coding:ekgCode.id</t>
   </si>
   <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.extension</t>
+  </si>
+  <si>
     <t>Observation.code.coding.extension</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.system</t>
+  </si>
+  <si>
     <t>Observation.code.coding.system</t>
   </si>
   <si>
-    <t>Loinc_CS</t>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:ekgCode.version</t>
   </si>
   <si>
     <t>Observation.code.coding.version</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.code</t>
+  </si>
+  <si>
     <t>Observation.code.coding.code</t>
   </si>
   <si>
     <t>11524-6</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.display</t>
+  </si>
+  <si>
     <t>Observation.code.coding.display</t>
   </si>
   <si>
     <t>EKG Study</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:ekgCode.userSelected</t>
   </si>
   <si>
     <t>Observation.code.coding.userSelected</t>
@@ -1981,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP76"/>
+  <dimension ref="A1:AP77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.17578125" customWidth="true" bestFit="true"/>
@@ -5888,7 +5918,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>82</v>
@@ -5952,16 +5982,14 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>226</v>
@@ -6002,15 +6030,17 @@
         <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -6022,19 +6052,23 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>210</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6082,19 +6116,19 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6103,10 +6137,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6117,21 +6151,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6143,17 +6177,15 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6190,31 +6222,31 @@
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6237,21 +6269,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6260,29 +6292,27 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>308</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6312,31 +6342,31 @@
         <v>83</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>83</v>
@@ -6345,10 +6375,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6359,10 +6389,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6370,7 +6400,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -6385,24 +6415,26 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6444,7 +6476,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6465,10 +6497,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6479,10 +6511,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6505,24 +6537,24 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>114</v>
+        <v>209</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>83</v>
@@ -6564,7 +6596,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6585,10 +6617,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6599,10 +6631,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6625,27 +6657,27 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>83</v>
@@ -6684,7 +6716,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6705,10 +6737,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6719,10 +6751,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6745,19 +6777,17 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6767,7 +6797,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -6806,7 +6836,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6827,10 +6857,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6841,10 +6871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6867,19 +6897,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6928,7 +6958,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6949,10 +6979,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6963,10 +6993,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6989,19 +7019,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7050,7 +7080,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7065,19 +7095,19 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7085,10 +7115,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7099,7 +7129,7 @@
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -7111,18 +7141,20 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7170,13 +7202,13 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
@@ -7185,19 +7217,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7205,21 +7237,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7231,20 +7263,18 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7292,13 +7322,13 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
@@ -7307,19 +7337,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>337</v>
+        <v>298</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7456,7 +7486,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7475,18 +7505,20 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7549,19 +7581,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7569,10 +7601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7583,7 +7615,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7595,20 +7627,18 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7656,13 +7686,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7671,19 +7701,19 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7691,10 +7721,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7705,7 +7735,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7717,19 +7747,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7778,25 +7808,25 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>373</v>
@@ -7805,10 +7835,10 @@
         <v>374</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>375</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
@@ -7836,22 +7866,22 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>201</v>
+        <v>377</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7876,13 +7906,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7909,7 +7939,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7918,10 +7948,10 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>384</v>
@@ -7930,26 +7960,26 @@
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>386</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7998,11 +8028,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8020,16 +8052,16 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8038,19 +8070,19 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>392</v>
+        <v>137</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
@@ -8062,7 +8094,7 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8081,7 +8113,7 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>396</v>
+        <v>201</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>397</v>
@@ -8118,13 +8150,11 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8160,27 +8190,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8191,7 +8221,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8203,18 +8233,20 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>201</v>
+        <v>406</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8238,37 +8270,37 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8280,19 +8312,19 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53">
@@ -8334,9 +8366,7 @@
       <c r="N53" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="O53" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8360,7 +8390,7 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="Y53" t="s" s="2">
         <v>416</v>
@@ -8402,27 +8432,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>83</v>
+        <v>418</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>83</v>
+        <v>421</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8445,18 +8475,20 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>421</v>
+        <v>201</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8480,13 +8512,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>83</v>
+        <v>426</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8504,7 +8536,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8522,27 +8554,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>427</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8565,16 +8597,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8624,7 +8656,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8642,27 +8674,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8673,7 +8705,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
@@ -8685,20 +8717,18 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8746,45 +8776,45 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>441</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8795,7 +8825,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -8807,16 +8837,20 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>209</v>
+        <v>447</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>210</v>
+        <v>448</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -8864,19 +8898,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>212</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>83</v>
+        <v>451</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8885,10 +8919,10 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>83</v>
+        <v>452</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>213</v>
+        <v>453</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8899,21 +8933,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
@@ -8925,17 +8959,15 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8984,19 +9016,19 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
@@ -9019,14 +9051,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>447</v>
+        <v>158</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9039,26 +9071,24 @@
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>448</v>
+        <v>215</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>449</v>
+        <v>216</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O59" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9106,7 +9136,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>218</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9130,7 +9160,7 @@
         <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9141,42 +9171,46 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>452</v>
+        <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9224,19 +9258,19 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>455</v>
+        <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>83</v>
@@ -9245,10 +9279,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>457</v>
+        <v>137</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9259,10 +9293,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9285,13 +9319,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9342,7 +9376,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9351,7 +9385,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9363,10 +9397,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9377,10 +9411,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9403,20 +9437,16 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>201</v>
+        <v>462</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9440,31 +9470,31 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="Z62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9473,7 +9503,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>83</v>
+        <v>465</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9482,13 +9512,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>469</v>
+        <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>393</v>
+        <v>471</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9499,10 +9529,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9513,7 +9543,7 @@
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>83</v>
@@ -9528,16 +9558,16 @@
         <v>201</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9562,13 +9592,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>405</v>
+        <v>118</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9586,13 +9616,13 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
@@ -9604,13 +9634,13 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9621,10 +9651,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9635,7 +9665,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -9647,17 +9677,19 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>479</v>
+        <v>201</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9682,13 +9714,13 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>83</v>
+        <v>486</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9706,13 +9738,13 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
@@ -9724,13 +9756,13 @@
         <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>83</v>
+        <v>480</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>483</v>
+        <v>403</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9741,10 +9773,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9767,16 +9799,18 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>209</v>
+        <v>489</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
@@ -9824,7 +9858,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9845,10 +9879,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9859,10 +9893,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9873,7 +9907,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -9882,20 +9916,18 @@
         <v>83</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>489</v>
+        <v>209</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -9944,13 +9976,13 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
@@ -9965,10 +9997,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9979,10 +10011,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10005,16 +10037,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10064,7 +10096,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10085,10 +10117,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10099,10 +10131,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10125,20 +10157,18 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>437</v>
+        <v>505</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>83</v>
       </c>
@@ -10186,7 +10216,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10207,10 +10237,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10221,10 +10251,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10235,7 +10265,7 @@
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>83</v>
@@ -10244,19 +10274,23 @@
         <v>83</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>209</v>
+        <v>447</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10304,19 +10338,19 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>212</v>
+        <v>509</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>83</v>
@@ -10325,10 +10359,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>83</v>
+        <v>513</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>213</v>
+        <v>514</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10339,21 +10373,21 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>83</v>
@@ -10365,17 +10399,15 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10424,19 +10456,19 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
@@ -10459,14 +10491,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>447</v>
+        <v>158</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10479,26 +10511,24 @@
         <v>83</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>448</v>
+        <v>215</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>449</v>
+        <v>216</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O71" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10546,7 +10576,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>450</v>
+        <v>218</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10570,7 +10600,7 @@
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10581,45 +10611,45 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>510</v>
+        <v>459</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>511</v>
+        <v>161</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>294</v>
+        <v>162</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10644,11 +10674,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10666,34 +10698,34 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>508</v>
+        <v>460</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>512</v>
+        <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -10701,10 +10733,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10712,7 +10744,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>94</v>
@@ -10727,19 +10759,19 @@
         <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>367</v>
+        <v>201</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>370</v>
+        <v>294</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10764,13 +10796,11 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10788,10 +10818,10 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>94</v>
@@ -10806,27 +10836,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>373</v>
+        <v>298</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>374</v>
+        <v>299</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>375</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10846,22 +10876,22 @@
         <v>83</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>201</v>
+        <v>377</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10886,13 +10916,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10910,7 +10940,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10919,7 +10949,7 @@
         <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>106</v>
@@ -10928,10 +10958,10 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>384</v>
@@ -10940,26 +10970,26 @@
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>386</v>
+        <v>83</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>83</v>
@@ -10974,16 +11004,16 @@
         <v>201</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>526</v>
+        <v>389</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11008,11 +11038,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11030,16 +11062,16 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11048,31 +11080,31 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>392</v>
+        <v>137</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11091,19 +11123,19 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11128,13 +11160,11 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11152,7 +11182,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11170,18 +11200,140 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>442</v>
+        <v>402</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>443</v>
+        <v>403</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="546">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-07</t>
+    <t>2024-11-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,6 +502,38 @@
   </si>
   <si>
     <t>心電図検査の所見が機械的に判定されたものであるかどうかを示す</t>
+  </si>
+  <si>
+    <t>Observation.extension:duration</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_Duration}
+</t>
+  </si>
+  <si>
+    <t>測定を行った時間(長さ)</t>
+  </si>
+  <si>
+    <t>心電図検査で測定が行われた時間を示す。</t>
+  </si>
+  <si>
+    <t>Observation.extension:stressType</t>
+  </si>
+  <si>
+    <t>stressType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_StressType}
+</t>
+  </si>
+  <si>
+    <t>負荷心電図種別</t>
+  </si>
+  <si>
+    <t>負荷心電図の種別を示す拡張である。</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -648,7 +680,7 @@
 </t>
   </si>
   <si>
-    <t>Observationリソースに対する分類コード。心電図検査には procedure が指定される。</t>
+    <t>Observationリソースに対する分類コード。心電図検査には通常 procedure が指定される。必要に応じてextraCategoryを仕様する</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
@@ -713,7 +745,7 @@
     <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
   </si>
   <si>
-    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+    <t>心電図検査は通常 procedure に分類される。</t>
   </si>
   <si>
     <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
@@ -732,28 +764,28 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory</t>
-  </si>
-  <si>
-    <t>simpleCategory</t>
-  </si>
-  <si>
-    <t>心電図検査は procedure に分類されている。</t>
-  </si>
-  <si>
-    <t>Observation.category.coding:simpleCategory.id</t>
+    <t>Observation.category.coding:electrocardiogram</t>
+  </si>
+  <si>
+    <t>electrocardiogram</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:electrocardiogram.id</t>
   </si>
   <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.extension</t>
+    <t>Observation.category.coding:electrocardiogram.extension</t>
   </si>
   <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.system</t>
+    <t>Observation.category.coding:electrocardiogram.system</t>
   </si>
   <si>
     <t>Observation.category.coding.system</t>
@@ -783,7 +815,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.version</t>
+    <t>Observation.category.coding:electrocardiogram.version</t>
   </si>
   <si>
     <t>Observation.category.coding.version</t>
@@ -807,7 +839,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.code</t>
+    <t>Observation.category.coding:electrocardiogram.code</t>
   </si>
   <si>
     <t>Observation.category.coding.code</t>
@@ -834,7 +866,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.display</t>
+    <t>Observation.category.coding:electrocardiogram.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -849,9 +881,6 @@
     <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
-    <t>Procedure</t>
-  </si>
-  <si>
     <t>Coding.display</t>
   </si>
   <si>
@@ -861,7 +890,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.userSelected</t>
+    <t>Observation.category.coding:electrocardiogram.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -892,6 +921,45 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
+    <t>Observation.category.coding:extraCategory</t>
+  </si>
+  <si>
+    <t>extraCategory</t>
+  </si>
+  <si>
+    <t>心電図検査について、負荷試験などの条件をつけた分類</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrocardiogramExtraCategory_CS</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.version</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.display</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.userSelected</t>
+  </si>
+  <si>
     <t>Observation.category.text</t>
   </si>
   <si>
@@ -926,13 +994,16 @@
     <t>心電図検査を示すコード</t>
   </si>
   <si>
-    <t>observationの意味を正しく理解するには、すべてのcode-valueペアと、さらに存在する場合にはcomponent.code-component.valueのペアが、考慮される必要がある。</t>
+    <t>心電図検査(LOINC: EKG Study)を示すLOINCコード 11524-6 を固定値として指定する。</t>
   </si>
   <si>
     <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
+    <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -962,64 +1033,11 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>Observation.code.coding:ekgCode</t>
-  </si>
-  <si>
-    <t>ekgCode</t>
-  </si>
-  <si>
-    <t>心電図検査(EKG Study)を示すLOINCコード 11524-6 を固定値として指定する。</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.system</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>11524-6</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.display</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.display</t>
-  </si>
-  <si>
-    <t>EKG Study</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.userSelected</t>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="11524-6"/&gt;
+  &lt;display value="EKG Study"/&gt;
+&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1306,9 +1324,6 @@
     <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
 ユースケースでは、ボディサイトを個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
@@ -1645,6 +1660,9 @@
   </si>
   <si>
     <t>心電図の各検査項目についてはLOINCなどの特定の用語集を利用することが推奨される。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2011,10 +2029,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP77"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.17578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.76953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3384,43 +3402,41 @@
         <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>83</v>
       </c>
@@ -3468,7 +3484,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3477,7 +3493,7 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>145</v>
@@ -3492,7 +3508,7 @@
         <v>83</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>83</v>
@@ -3503,12 +3519,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>83</v>
       </c>
@@ -3517,7 +3535,7 @@
         <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>83</v>
@@ -3526,21 +3544,19 @@
         <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>166</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>83</v>
       </c>
@@ -3588,7 +3604,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3597,25 +3613,25 @@
         <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>83</v>
@@ -3623,14 +3639,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3643,23 +3659,25 @@
         <v>83</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>83</v>
@@ -3708,7 +3726,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3720,19 +3738,19 @@
         <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>83</v>
@@ -3743,14 +3761,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3769,18 +3787,18 @@
         <v>95</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
       </c>
@@ -3828,7 +3846,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3843,19 +3861,19 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3863,45 +3881,43 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3926,13 +3942,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3950,13 +3966,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3965,19 +3981,19 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3985,14 +4001,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4008,23 +4024,21 @@
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>83</v>
       </c>
@@ -4048,11 +4062,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4070,7 +4086,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4085,19 +4101,19 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -4105,10 +4121,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4116,7 +4132,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>94</v>
@@ -4125,22 +4141,26 @@
         <v>83</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4164,13 +4184,13 @@
         <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>83</v>
@@ -4188,10 +4208,10 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>94</v>
@@ -4200,22 +4220,22 @@
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4223,14 +4243,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4249,18 +4269,20 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4284,31 +4306,29 @@
         <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4320,7 +4340,7 @@
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
@@ -4332,10 +4352,10 @@
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4343,10 +4363,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4357,7 +4377,7 @@
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>83</v>
@@ -4366,23 +4386,19 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4418,29 +4434,31 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>83</v>
@@ -4449,10 +4467,10 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4463,23 +4481,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>83</v>
@@ -4488,23 +4504,21 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4528,29 +4542,31 @@
         <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4562,7 +4578,7 @@
         <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>83</v>
@@ -4571,10 +4587,10 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4585,10 +4601,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4596,10 +4612,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4608,19 +4624,23 @@
         <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4656,31 +4676,29 @@
         <v>83</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>83</v>
@@ -4689,10 +4707,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4703,21 +4721,23 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>83</v>
@@ -4726,21 +4746,23 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4764,31 +4786,29 @@
         <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4800,7 +4820,7 @@
         <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>83</v>
@@ -4809,10 +4829,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4823,10 +4843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4834,7 +4854,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
@@ -4846,29 +4866,25 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4910,7 +4926,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4922,7 +4938,7 @@
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
@@ -4931,10 +4947,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4945,21 +4961,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4968,19 +4984,19 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5018,31 +5034,31 @@
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>83</v>
@@ -5051,10 +5067,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5065,10 +5081,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5076,7 +5092,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>94</v>
@@ -5091,24 +5107,26 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -5150,7 +5168,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5171,10 +5189,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5185,10 +5203,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5211,24 +5229,24 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>83</v>
@@ -5270,7 +5288,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5291,10 +5309,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5305,10 +5323,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5331,26 +5349,24 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>274</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>83</v>
@@ -5392,7 +5408,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5413,10 +5429,10 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -5427,10 +5443,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5453,19 +5469,17 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5514,7 +5528,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5535,10 +5549,10 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5549,18 +5563,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
@@ -5575,19 +5589,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>283</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5612,11 +5626,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5634,10 +5650,10 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>94</v>
@@ -5649,32 +5665,34 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5692,19 +5710,23 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5728,13 +5750,11 @@
         <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>83</v>
@@ -5752,19 +5772,19 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5773,10 +5793,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5787,21 +5807,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5813,17 +5833,15 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5860,31 +5878,31 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -5896,7 +5914,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5907,18 +5925,18 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>245</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>82</v>
@@ -5930,23 +5948,21 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5982,9 +5998,11 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5992,7 +6010,7 @@
         <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6004,7 +6022,7 @@
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6013,10 +6031,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6027,14 +6045,12 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6055,19 +6071,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>248</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6077,7 +6093,7 @@
         <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>83</v>
@@ -6116,13 +6132,13 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
@@ -6137,10 +6153,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6151,10 +6167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6174,18 +6190,20 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6234,7 +6252,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6246,7 +6264,7 @@
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6255,10 +6273,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6269,21 +6287,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6292,21 +6310,21 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>215</v>
+        <v>266</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6342,31 +6360,31 @@
         <v>83</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>83</v>
@@ -6375,10 +6393,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6389,10 +6407,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>313</v>
+        <v>274</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6400,7 +6418,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -6415,26 +6433,24 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6476,7 +6492,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6497,10 +6513,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6511,10 +6527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6537,18 +6553,20 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6596,7 +6614,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6617,10 +6635,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6631,10 +6649,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6657,24 +6675,26 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>256</v>
+        <v>305</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>83</v>
@@ -6716,7 +6736,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>260</v>
+        <v>309</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6737,10 +6757,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>261</v>
+        <v>310</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6751,18 +6771,18 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>94</v>
@@ -6777,17 +6797,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>265</v>
+        <v>314</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>267</v>
+        <v>316</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6797,7 +6819,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -6812,13 +6834,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6836,10 +6858,10 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>94</v>
@@ -6851,30 +6873,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>270</v>
+        <v>321</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>271</v>
+        <v>322</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6894,23 +6916,19 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>275</v>
+        <v>220</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6958,7 +6976,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6970,7 +6988,7 @@
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -6979,10 +6997,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6993,21 +7011,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -7016,23 +7034,21 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7068,31 +7084,31 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7101,10 +7117,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7115,10 +7131,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7129,7 +7145,7 @@
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -7141,26 +7157,26 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>327</v>
+        <v>230</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>231</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
+        <v>232</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>329</v>
+        <v>241</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>330</v>
+        <v>234</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>83</v>
@@ -7202,13 +7218,13 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>236</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
@@ -7217,19 +7233,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>332</v>
+        <v>237</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7237,10 +7253,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7251,7 +7267,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7263,18 +7279,20 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>336</v>
+        <v>219</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7322,13 +7340,13 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
@@ -7343,13 +7361,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7357,14 +7375,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7383,19 +7401,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7444,7 +7462,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7459,19 +7477,19 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7479,21 +7497,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>83</v>
@@ -7505,20 +7523,18 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7566,13 +7582,13 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>83</v>
@@ -7581,19 +7597,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7601,14 +7617,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7627,18 +7643,20 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7686,7 +7704,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7701,19 +7719,19 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>350</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7721,21 +7739,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7747,19 +7765,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7808,13 +7826,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7823,19 +7841,19 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -7843,10 +7861,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7869,20 +7887,18 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7930,7 +7946,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7939,7 +7955,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7948,27 +7964,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>83</v>
+        <v>370</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7979,7 +7995,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7988,22 +8004,22 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8028,13 +8044,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8052,34 +8068,34 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>137</v>
+        <v>377</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8087,21 +8103,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -8110,22 +8126,22 @@
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>201</v>
+        <v>381</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8150,11 +8166,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8172,16 +8190,16 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8190,27 +8208,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>404</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8221,7 +8239,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8233,19 +8251,19 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>406</v>
+        <v>211</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8270,13 +8288,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8294,16 +8312,16 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8315,10 +8333,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>410</v>
+        <v>137</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8329,21 +8347,21 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8355,18 +8373,20 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8390,13 +8410,11 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8414,13 +8432,13 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
@@ -8432,27 +8450,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8463,7 +8481,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8475,19 +8493,19 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>201</v>
+        <v>410</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8512,13 +8530,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>426</v>
+        <v>83</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>427</v>
+        <v>83</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8536,13 +8554,13 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
@@ -8557,10 +8575,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8571,10 +8589,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8597,16 +8615,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>431</v>
+        <v>211</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8632,13 +8650,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8656,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8674,27 +8692,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>437</v>
+        <v>424</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8717,18 +8735,20 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>439</v>
+        <v>211</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8752,13 +8772,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>83</v>
+        <v>429</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8776,7 +8796,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8794,27 +8814,27 @@
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>445</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8825,7 +8845,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -8837,20 +8857,18 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -8898,45 +8916,45 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>451</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>83</v>
+        <v>437</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>83</v>
+        <v>440</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8959,15 +8977,17 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>209</v>
+        <v>442</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>210</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9016,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>212</v>
+        <v>441</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9028,37 +9048,37 @@
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>213</v>
+        <v>447</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9077,18 +9097,20 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>139</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>215</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>216</v>
+        <v>451</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9136,7 +9158,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>218</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9148,7 +9170,7 @@
         <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>454</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>83</v>
@@ -9157,10 +9179,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>213</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9171,46 +9193,42 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>220</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9258,19 +9276,19 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>460</v>
+        <v>222</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>83</v>
@@ -9282,7 +9300,7 @@
         <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9293,21 +9311,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>83</v>
@@ -9319,15 +9337,17 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>462</v>
+        <v>139</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>225</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9376,19 +9396,19 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>228</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>83</v>
@@ -9397,10 +9417,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>467</v>
+        <v>223</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9411,42 +9431,46 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="N62" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9494,19 +9518,19 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -9515,10 +9539,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>471</v>
+        <v>137</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9529,10 +9553,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9555,20 +9579,16 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>201</v>
+        <v>465</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -9592,13 +9612,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>477</v>
+        <v>83</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>478</v>
+        <v>83</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9616,7 +9636,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9625,7 +9645,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -9634,13 +9654,13 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>403</v>
+        <v>470</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9651,10 +9671,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9665,7 +9685,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -9677,20 +9697,16 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>201</v>
+        <v>465</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9714,13 +9730,13 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>486</v>
+        <v>83</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9738,16 +9754,16 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -9756,13 +9772,13 @@
         <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9773,10 +9789,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9799,17 +9815,19 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>489</v>
+        <v>211</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9834,13 +9852,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>83</v>
+        <v>480</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>83</v>
+        <v>481</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9858,7 +9876,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9876,13 +9894,13 @@
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>83</v>
+        <v>482</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>83</v>
+        <v>483</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>493</v>
+        <v>407</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9893,10 +9911,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9907,7 +9925,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -9919,16 +9937,20 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
@@ -9952,13 +9974,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>83</v>
+        <v>489</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>83</v>
+        <v>490</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -9976,13 +9998,13 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
@@ -9994,13 +10016,13 @@
         <v>83</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>83</v>
+        <v>482</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>497</v>
+        <v>407</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10011,10 +10033,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10025,7 +10047,7 @@
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>83</v>
@@ -10034,21 +10056,21 @@
         <v>83</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
@@ -10096,13 +10118,13 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>83</v>
@@ -10117,10 +10139,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10131,10 +10153,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10145,7 +10167,7 @@
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>83</v>
@@ -10154,20 +10176,18 @@
         <v>83</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>505</v>
+        <v>219</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10216,13 +10236,13 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>83</v>
@@ -10237,10 +10257,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10251,10 +10271,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10277,20 +10297,18 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>447</v>
+        <v>502</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10338,7 +10356,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10359,10 +10377,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10373,10 +10391,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10387,7 +10405,7 @@
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>83</v>
@@ -10396,18 +10414,20 @@
         <v>83</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>209</v>
+        <v>508</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>210</v>
+        <v>509</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10456,19 +10476,19 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>212</v>
+        <v>507</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
@@ -10477,10 +10497,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>83</v>
+        <v>505</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>213</v>
+        <v>511</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10491,14 +10511,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10514,21 +10534,23 @@
         <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>139</v>
+        <v>450</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>216</v>
+        <v>513</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10576,7 +10598,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>218</v>
+        <v>512</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10588,7 +10610,7 @@
         <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>83</v>
@@ -10597,10 +10619,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>83</v>
+        <v>516</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>213</v>
+        <v>517</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10611,46 +10633,42 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
+        <v>220</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
@@ -10698,19 +10716,19 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>460</v>
+        <v>222</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -10722,7 +10740,7 @@
         <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10733,21 +10751,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
@@ -10756,23 +10774,21 @@
         <v>83</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>225</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>226</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10796,11 +10812,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10818,34 +10836,34 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>228</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>522</v>
+        <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
@@ -10853,45 +10871,45 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>377</v>
+        <v>139</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>524</v>
+        <v>461</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>525</v>
+        <v>462</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>526</v>
+        <v>171</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>380</v>
+        <v>172</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10940,45 +10958,45 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>527</v>
+        <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>384</v>
+        <v>137</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10986,7 +11004,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>94</v>
@@ -10998,22 +11016,22 @@
         <v>83</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11038,13 +11056,11 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>392</v>
+        <v>525</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11062,16 +11078,16 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11080,16 +11096,16 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>83</v>
+        <v>526</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>137</v>
+        <v>321</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -11097,21 +11113,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>83</v>
@@ -11120,22 +11136,22 @@
         <v>83</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>201</v>
+        <v>381</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>536</v>
+        <v>384</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11160,11 +11176,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11182,13 +11200,13 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>83</v>
@@ -11200,27 +11218,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>401</v>
+        <v>531</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>404</v>
+        <v>389</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11231,7 +11249,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11243,19 +11261,19 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>541</v>
+        <v>393</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11280,13 +11298,13 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -11304,16 +11322,16 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -11325,15 +11343,257 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>452</v>
+        <v>137</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>453</v>
+        <v>398</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Y78" s="2"/>
+      <c r="Z78" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
     </row>
